--- a/output/芳賀赤十字病院_随意契約_X線関連.xlsx
+++ b/output/芳賀赤十字病院_随意契約_X線関連.xlsx
@@ -837,7 +837,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>不明（アズサイエンス株式会社北関東支店 医療宇都宮営業所栃木県宇都宮市平出町385-15〜フクダ電子宇都宮市砥上町1649-2）</t>
+          <t>不明（日本電気株式会社東京都港区芝四丁目14－1〜フクダ電子宇都宮市砥上町1649-2）</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">

--- a/output/芳賀赤十字病院_随意契約_X線関連.xlsx
+++ b/output/芳賀赤十字病院_随意契約_X線関連.xlsx
@@ -74,13 +74,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -532,30 +535,24 @@
           <t>血管造影撮影装置保守</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>事務部管財課真岡中萩ニ丁目10番地１</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>令和7年4月1日</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>日成メディカル宇都宮市問屋町3426-39</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>16,500,000</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
+      <c r="F4" s="4" t="n">
+        <v>16500000</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -580,30 +577,24 @@
           <t>富士フイルムＦＰＤ（フラットパネルディスプレイ）装置及びＸ線回診車（フラットパネル含む）の保守契約（更新）</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>事務部管財課真岡中萩ニ丁目10番地１</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>令和7年4月1日</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>富士フイルムメディカル株式会社北関東支社さいたま市大宮区浅間町2-240</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>6,578,000</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
+      <c r="F5" s="4" t="n">
+        <v>6578000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -628,30 +619,24 @@
           <t>一般撮影装置X線電圧発生器</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>事務部管財課真岡中萩ニ丁目10番地１</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>令和6年5月26日</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>キヤノンメディカルシステムズ栃木県大田原市下石上1385番地</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>3,685,000</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
+      <c r="F6" s="4" t="n">
+        <v>3685000</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -697,17 +682,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>装置カテゴリ</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>該当件数</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -781,24 +766,24 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>データソース（随意契約に関する公示 PDF）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>対象年度</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>掲載件数</t>
         </is>
@@ -807,7 +792,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>不明（日本光電工業株式会社宇都宮市横田新町12-6〜サンメディックス株式会社宇都宮市細谷町388-1）</t>
+          <t>不明（令和7年6月21日〜令和7年7月31日）</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -837,7 +822,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>不明（日本電気株式会社東京都港区芝四丁目14－1〜フクダ電子宇都宮市砥上町1649-2）</t>
+          <t>不明（令和6年7月30日〜令和7年3月31日）</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">

--- a/output/芳賀赤十字病院_随意契約_X線関連.xlsx
+++ b/output/芳賀赤十字病院_随意契約_X線関連.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -701,59 +701,55 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>透視撮影台（X線テレビ）</t>
+          <t>一般撮影（レントゲン）</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>公表された随意契約に該当なし</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>血管撮影（CVS、アンギオ）</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>公表された随意契約に該当なし</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>公表された随意契約に該当なし</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>回診用X線装置</t>
+          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
